--- a/analizator-kredytowy/src/test.xlsx
+++ b/analizator-kredytowy/src/test.xlsx
@@ -1,26 +1,110 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\php_websites\analizator-kredytowy\src\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{409B76A1-DAE6-417C-AFD6-315775BE20D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+  <si>
+    <t>maxMonthlyDebt</t>
+  </si>
+  <si>
+    <t>maxRata</t>
+  </si>
+  <si>
+    <t>DTI</t>
+  </si>
+  <si>
+    <t>minimalne wydatki</t>
+  </si>
+  <si>
+    <t>osoby</t>
+  </si>
+  <si>
+    <t>suma długu</t>
+  </si>
+  <si>
+    <t>max total debt</t>
+  </si>
+  <si>
+    <t>okres</t>
+  </si>
+  <si>
+    <t>CURRENT</t>
+  </si>
+  <si>
+    <t>CORRECT</t>
+  </si>
+  <si>
+    <t>okres msc</t>
+  </si>
+  <si>
+    <t>RRSO</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>bufor</t>
+  </si>
+  <si>
+    <t>zdolnosc</t>
+  </si>
+  <si>
+    <t>rata malejąca pierwsza</t>
+  </si>
+  <si>
+    <t>rata stała</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _z_ł_-;\-* #,##0.00\ _z_ł_-;_-* &quot;-&quot;??\ _z_ł_-;_-@_-"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -46,14 +130,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="3">
+    <cellStyle name="Dziesiętny" xfId="1" builtinId="3"/>
+    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
+    <cellStyle name="Procentowy" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +422,168 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="C2:F22"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="21.81640625" customWidth="1"/>
+    <col min="4" max="4" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>1860.38</v>
+      </c>
+    </row>
+    <row r="9" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="1">
+        <f>0.65</f>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="10" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11">
+        <f>12*D10</f>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="12" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="4">
+        <f>0.0713</f>
+        <v>7.1300000000000002E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <f>8255</f>
+        <v>8255</v>
+      </c>
+    </row>
+    <row r="16" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2">
+        <f>D15-D6-D8*D7</f>
+        <v>4234.24</v>
+      </c>
+    </row>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="2">
+        <f>D10*D16*1</f>
+        <v>127027.2</v>
+      </c>
+      <c r="E17" s="3">
+        <f>D11*D16</f>
+        <v>1524326.3999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="4">
+        <f>(D12+D13)/12</f>
+        <v>5.9416666666666671E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="2">
+        <f>D16*((1+D18)^D11-1)/(D18*(1+D18)^D11)</f>
+        <v>628173.29283456563</v>
+      </c>
+      <c r="E19" s="3"/>
+    </row>
+    <row r="21" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C21" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="3">
+        <f>E17/D11</f>
+        <v>4234.24</v>
+      </c>
+    </row>
+    <row r="22" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="3">
+        <f>D16/(1/D11+D18)</f>
+        <v>485608.92003822868</v>
+      </c>
+      <c r="E22" s="3">
+        <f>D19*D12/12+F22</f>
+        <v>5477.3221283547264</v>
+      </c>
+      <c r="F22" s="3">
+        <f>D19/D11</f>
+        <v>1744.9258134293489</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>